--- a/Data/Heat Pump.xlsx
+++ b/Data/Heat Pump.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/Progressive Hedging /Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/Benders-Decomposition/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31DDC89F-5CF4-2645-8FF3-C0CEDFBF5C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04CA51E-AC3B-3D4D-9D26-CBA25CA484C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
   </bookViews>
   <sheets>
     <sheet name="Initial values" sheetId="7" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>Metrics</t>
   </si>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>Heat transfer capacity</t>
+  </si>
+  <si>
+    <t>linear</t>
   </si>
 </sst>
 </file>
@@ -123,8 +126,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -475,15 +482,15 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5">
-        <v>0</v>
+      <c r="B5" s="2">
+        <v>2258</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -508,7 +515,7 @@
         <v>15</v>
       </c>
       <c r="B8">
-        <v>10000</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -570,15 +577,15 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>0.13489999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
-        <v>0</v>
+      <c r="B4" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -586,8 +593,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <f>EXP(-B3)</f>
-        <v>1</v>
+        <v>0.87380000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -595,8 +601,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <f>EXP(B4)</f>
-        <v>1</v>
+        <v>0.15551999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Heat Pump.xlsx
+++ b/Data/Heat Pump.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/Benders-Decomposition/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04CA51E-AC3B-3D4D-9D26-CBA25CA484C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62A30A5-5CBF-AD4E-8663-8E6A7FB338C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20060" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
   </bookViews>
   <sheets>
     <sheet name="Initial values" sheetId="7" r:id="rId1"/>
@@ -498,7 +498,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
